--- a/resources/templates/standard/L1100-03.xlsx
+++ b/resources/templates/standard/L1100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">입회검수
 CHECK SHEET</t>
@@ -676,12 +679,14 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -805,10 +810,10 @@
     <row r="4" ht="17.5" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -821,7 +826,7 @@
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
@@ -835,13 +840,13 @@
       <c r="X4" s="11"/>
       <c r="Y4" s="12"/>
       <c r="Z4" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA4" s="13"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="14"/>
       <c r="AD4" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE4" s="11"/>
       <c r="AF4" s="11"/>
@@ -1983,19 +1988,19 @@
       <c r="AH31" s="5"/>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK31" s="23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL31" s="23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM31" s="23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN31" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
